--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -149,7 +149,6 @@
         <sz val="10"/>
         <rFont val="Noto Sans SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">雪莉是最棒的巡逻员：可靠、顽强、擅长使用霰弹枪。她实在不明白柯尔特为什么一定要抢她的风头</t>
     </r>
@@ -158,16 +157,21 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">......</t>
     </r>
   </si>
   <si>
+    <t xml:space="preserve">BasicFemaleDefault</t>
+  </si>
+  <si>
     <t xml:space="preserve">公牛</t>
   </si>
   <si>
     <t xml:space="preserve">公牛没有年轻时那么无忧无虑，也没有那么爱惹事了。但如果有人敢挑衅，他还是会毫不犹豫地把他们撞飞！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BasicMaleDefault</t>
   </si>
 </sst>
 </file>
@@ -177,7 +181,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
@@ -237,9 +241,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -306,7 +314,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -348,6 +356,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -776,8 +788,11 @@
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="11" t="s">
         <v>34</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>1</v>
@@ -812,10 +827,13 @@
         <v>201</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -64,6 +64,12 @@
     <t xml:space="preserve">UnlockPrice</t>
   </si>
   <si>
+    <t xml:space="preserve">CollisionRadius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionHeight</t>
+  </si>
+  <si>
     <t xml:space="preserve">##type</t>
   </si>
   <si>
@@ -71,6 +77,9 @@
   </si>
   <si>
     <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">float</t>
   </si>
   <si>
     <t xml:space="preserve">##group</t>
@@ -141,6 +150,12 @@
     <t xml:space="preserve">解锁价格</t>
   </si>
   <si>
+    <t xml:space="preserve">碰撞半径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞高度</t>
+  </si>
+  <si>
     <t xml:space="preserve">雪莉</t>
   </si>
   <si>
@@ -149,6 +164,7 @@
         <sz val="10"/>
         <rFont val="Noto Sans SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">雪莉是最棒的巡逻员：可靠、顽强、擅长使用霰弹枪。她实在不明白柯尔特为什么一定要抢她的风头</t>
     </r>
@@ -157,6 +173,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">......</t>
     </r>
@@ -172,6 +189,24 @@
   </si>
   <si>
     <t xml:space="preserve">BasicMaleDefault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">武士</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这是个武士</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SamuraiDefault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特是型秒乐园的大明星！他英俊潇洒，魅力四射，还会花式转枪，这些让他赢得了所有观众的心，不过雪莉除外。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VeteranDefault</t>
   </si>
 </sst>
 </file>
@@ -181,7 +216,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
@@ -241,13 +276,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Noto Sans SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -359,7 +390,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -610,7 +641,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
@@ -621,7 +652,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="26.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -668,64 +699,76 @@
       <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -736,49 +779,57 @@
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -786,13 +837,13 @@
         <v>101</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>1</v>
@@ -820,6 +871,12 @@
       </c>
       <c r="N5" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -827,13 +884,13 @@
         <v>201</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
@@ -861,6 +918,106 @@
       </c>
       <c r="N6" s="1" t="n">
         <v>10</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>30101</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>30102</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>30103</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
+        <v>401</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>40101</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>40102</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>40103</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -207,6 +207,15 @@
   </si>
   <si>
     <t xml:space="preserve">VeteranDefault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卡尔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">牛逼卡尔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChickenDefault</t>
   </si>
 </sst>
 </file>
@@ -641,7 +650,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
@@ -958,7 +967,7 @@
         <v>3500</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>4</v>
@@ -1005,7 +1014,7 @@
         <v>4000</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>3</v>
@@ -1017,6 +1026,53 @@
         <v>0.3</v>
       </c>
       <c r="P8" s="1" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1001001</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>1001002</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>1001003</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>4500</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P9" s="1" t="n">
         <v>1.2</v>
       </c>
     </row>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="BrawlHero" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -20,21 +20,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>ModelPath</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
+  <si>
+    <t xml:space="preserve">##var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModelPath</t>
   </si>
   <si>
     <t xml:space="preserve">Rarity </t>
@@ -43,70 +43,67 @@
     <t xml:space="preserve">Role </t>
   </si>
   <si>
-    <t>NormalAttackSkillId</t>
+    <t xml:space="preserve">NormalAttackSkillId</t>
   </si>
   <si>
     <t xml:space="preserve">SuperSkillId </t>
   </si>
   <si>
-    <t>SpecialSkillId</t>
-  </si>
-  <si>
-    <t>BaseHp</t>
-  </si>
-  <si>
-    <t>HpGrowthPerLevel</t>
-  </si>
-  <si>
-    <t>MoveSpeedTier</t>
-  </si>
-  <si>
-    <t>UnlockPrice</t>
-  </si>
-  <si>
-    <t>CollisionRadius</t>
-  </si>
-  <si>
-    <t>CollisionHeight</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>英雄 ID</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>模型路径</t>
+    <t xml:space="preserve">SpecialSkillId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HpGrowthPerLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoveSpeedTier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnlockPrice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionRadius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionHeight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##</t>
+  </si>
+  <si>
+    <t xml:space="preserve">英雄 ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">描述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模型路径</t>
   </si>
   <si>
     <t xml:space="preserve">稀有度
@@ -129,13 +126,13 @@
 7 刺客</t>
   </si>
   <si>
-    <t>普攻攻击ID</t>
-  </si>
-  <si>
-    <t>超级技能ID</t>
-  </si>
-  <si>
-    <t>特殊技能ID</t>
+    <t xml:space="preserve">普攻攻击ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">超级技能ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特殊技能ID</t>
   </si>
   <si>
     <t xml:space="preserve">1 级基础生命值
@@ -153,94 +150,103 @@
 4 非常快</t>
   </si>
   <si>
-    <t>解锁价格</t>
-  </si>
-  <si>
-    <t>碰撞半径</t>
-  </si>
-  <si>
-    <t>碰撞高度</t>
-  </si>
-  <si>
-    <t>初始英雄等级，至少1</t>
-  </si>
-  <si>
-    <t>雪莉</t>
+    <t xml:space="preserve">解锁价格</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞半径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞高度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">初始英雄等级，至少1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪莉</t>
   </si>
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
         <rFont val="Noto Sans SC"/>
+        <family val="2"/>
         <charset val="1"/>
-        <family val="2"/>
-        <sz val="10"/>
       </rPr>
-      <t>雪莉是最棒的巡逻员：可靠、顽强、擅长使用霰弹枪。她实在不明白柯尔特为什么一定要抢她的风头</t>
+      <t xml:space="preserve">雪莉是最棒的巡逻员：可靠、顽强、擅长使用霰弹枪。她实在不明白柯尔特为什么一定要抢她的风头</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <charset val="1"/>
-        <family val="2"/>
-        <sz val="10"/>
       </rPr>
-      <t>......</t>
+      <t xml:space="preserve">......</t>
     </r>
   </si>
   <si>
-    <t>BasicFemaleDefault</t>
-  </si>
-  <si>
-    <t>公牛</t>
-  </si>
-  <si>
-    <t>公牛没有年轻时那么无忧无虑，也没有那么爱惹事了。但如果有人敢挑衅，他还是会毫不犹豫地把他们撞飞！</t>
-  </si>
-  <si>
-    <t>BasicMaleDefault</t>
-  </si>
-  <si>
-    <t>武士</t>
-  </si>
-  <si>
-    <t>这是个武士</t>
-  </si>
-  <si>
-    <t>SamuraiDefault</t>
-  </si>
-  <si>
-    <t>柯尔特</t>
-  </si>
-  <si>
-    <t>柯尔特是型秒乐园的大明星！他英俊潇洒，魅力四射，还会花式转枪，这些让他赢得了所有观众的心，不过雪莉除外。</t>
-  </si>
-  <si>
-    <t>VeteranDefault</t>
-  </si>
-  <si>
-    <t>卡尔</t>
-  </si>
-  <si>
-    <t>牛逼卡尔</t>
-  </si>
-  <si>
-    <t>ChickenDefault</t>
+    <t xml:space="preserve">BasicFemaleDefault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公牛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公牛没有年轻时那么无忧无虑，也没有那么爱惹事了。但如果有人敢挑衅，他还是会毫不犹豫地把他们撞飞！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BasicMaleDefault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">武士</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这是个武士</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SamuraiDefault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特是型秒乐园的大明星！他英俊潇洒，魅力四射，还会花式转枪，这些让他赢得了所有观众的心，不过雪莉除外。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VeteranDefault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卡尔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">牛逼卡尔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChickenDefault</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -254,7 +260,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -262,7 +268,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -281,6 +287,12 @@
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -311,7 +323,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="1" diagonalDown="1">
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -319,49 +331,93 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
-    <cellStyle name="Normal" xfId="6"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -596,26 +652,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1" style="1"/>
-    <col min="3" max="3" width="11.54" customWidth="1" style="1"/>
-    <col min="4" max="5" width="26" customWidth="1" style="2"/>
-    <col min="6" max="6" width="14.33" customWidth="1" style="1"/>
-    <col min="7" max="7" width="16.27" customWidth="1" style="1"/>
-    <col min="8" max="8" width="21.28" customWidth="1" style="1"/>
-    <col min="9" max="12" width="18" customWidth="1" style="1"/>
-    <col min="13" max="13" width="26.57" customWidth="1" style="1"/>
-    <col min="14" max="16" width="18" customWidth="1" style="1"/>
-    <col min="16382" max="16384" width="11.53" customWidth="1" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="26.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="21.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -664,11 +721,11 @@
       <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
@@ -717,11 +774,11 @@
       <c r="P2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="0" t="s">
+      <c r="Q2" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
@@ -746,310 +803,308 @@
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
-      <c r="Q3" s="0" t="s">
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="4" ht="121.6" customHeight="1">
-      <c r="A4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="9" t="s">
+    <row r="5" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>10101</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>10102</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>10103</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>3900</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>390</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>20101</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>20102</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>20103</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>30101</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>30102</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>30103</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>350</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
+        <v>401</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>40101</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>40102</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>40103</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q4" s="0" t="s">
-        <v>40</v>
+      <c r="O8" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" ht="49.25">
-      <c r="B5" s="1">
-        <v>101</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="1">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1001001</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>1001002</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>1001003</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>4500</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="M9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>10101</v>
-      </c>
-      <c r="I5" s="1">
-        <v>10102</v>
-      </c>
-      <c r="J5" s="1">
-        <v>10103</v>
-      </c>
-      <c r="K5" s="1">
-        <v>3900</v>
-      </c>
-      <c r="L5" s="1">
-        <v>390</v>
-      </c>
-      <c r="M5" s="1">
-        <v>3</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
+      <c r="N9" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="O9" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P9" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q5" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="49.25">
-      <c r="B6" s="1">
-        <v>201</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20101</v>
-      </c>
-      <c r="I6" s="1">
-        <v>20102</v>
-      </c>
-      <c r="J6" s="1">
-        <v>20103</v>
-      </c>
-      <c r="K6" s="1">
-        <v>5000</v>
-      </c>
-      <c r="L6" s="1">
-        <v>500</v>
-      </c>
-      <c r="M6" s="1">
-        <v>3</v>
-      </c>
-      <c r="N6" s="1">
-        <v>10</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="P6" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="Q6" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="15">
-      <c r="B7" s="1">
-        <v>301</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="1">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1">
-        <v>7</v>
-      </c>
-      <c r="H7" s="1">
-        <v>30101</v>
-      </c>
-      <c r="I7" s="1">
-        <v>30102</v>
-      </c>
-      <c r="J7" s="1">
-        <v>30103</v>
-      </c>
-      <c r="K7" s="1">
-        <v>3500</v>
-      </c>
-      <c r="L7" s="1">
-        <v>350</v>
-      </c>
-      <c r="M7" s="1">
-        <v>4</v>
-      </c>
-      <c r="N7" s="1">
-        <v>20</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="P7" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="Q7" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="49.25">
-      <c r="B8" s="1">
-        <v>401</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1">
-        <v>4</v>
-      </c>
-      <c r="H8" s="1">
-        <v>40101</v>
-      </c>
-      <c r="I8" s="1">
-        <v>40102</v>
-      </c>
-      <c r="J8" s="1">
-        <v>40103</v>
-      </c>
-      <c r="K8" s="1">
-        <v>4000</v>
-      </c>
-      <c r="L8" s="1">
-        <v>400</v>
-      </c>
-      <c r="M8" s="1">
-        <v>3</v>
-      </c>
-      <c r="N8" s="1">
-        <v>30</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="P8" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="Q8" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="15">
-      <c r="B9" s="1">
-        <v>1001</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="1">
-        <v>6</v>
-      </c>
-      <c r="G9" s="1">
-        <v>6</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1001001</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1001002</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1001003</v>
-      </c>
-      <c r="K9" s="1">
-        <v>4500</v>
-      </c>
-      <c r="L9" s="1">
-        <v>450</v>
-      </c>
-      <c r="M9" s="1">
-        <v>1</v>
-      </c>
-      <c r="N9" s="1">
-        <v>100</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="P9" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="Q9" s="0">
+      <c r="Q9" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1062,9 +1117,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -223,6 +223,12 @@
   <si>
     <t xml:space="preserve">ChickenDefault</t>
   </si>
+  <si>
+    <t xml:space="preserve">艾尔·普里莫</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾尔·普里莫以迅雷之势连续打出4记愤怒铁拳。这墨西哥劲辣红椒味的拳头可以把对手打得满地找牙！</t>
+  </si>
 </sst>
 </file>
 
@@ -231,7 +237,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
@@ -295,6 +301,11 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -360,7 +371,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -406,6 +417,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -656,7 +671,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
@@ -1108,6 +1123,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlHero.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="BrawlHero" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -20,21 +20,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
-  <si>
-    <t xml:space="preserve">##var</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ModelPath</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ModelPath</t>
   </si>
   <si>
     <t xml:space="preserve">Rarity </t>
@@ -43,67 +43,67 @@
     <t xml:space="preserve">Role </t>
   </si>
   <si>
-    <t xml:space="preserve">NormalAttackSkillId</t>
+    <t>NormalAttackSkillId</t>
   </si>
   <si>
     <t xml:space="preserve">SuperSkillId </t>
   </si>
   <si>
-    <t xml:space="preserve">SpecialSkillId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BaseHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HpGrowthPerLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MoveSpeedTier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UnlockPrice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CollisionRadius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CollisionHeight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">float</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##</t>
-  </si>
-  <si>
-    <t xml:space="preserve">英雄 ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">名字</t>
-  </si>
-  <si>
-    <t xml:space="preserve">描述</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模型路径</t>
+    <t>SpecialSkillId</t>
+  </si>
+  <si>
+    <t>BaseHp</t>
+  </si>
+  <si>
+    <t>HpGrowthPerLevel</t>
+  </si>
+  <si>
+    <t>MoveSpeedTier</t>
+  </si>
+  <si>
+    <t>UnlockPrice</t>
+  </si>
+  <si>
+    <t>CollisionRadius</t>
+  </si>
+  <si>
+    <t>CollisionHeight</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>英雄 ID</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>模型路径</t>
   </si>
   <si>
     <t xml:space="preserve">稀有度
@@ -126,13 +126,13 @@
 7 刺客</t>
   </si>
   <si>
-    <t xml:space="preserve">普攻攻击ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">超级技能ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特殊技能ID</t>
+    <t>普攻攻击ID</t>
+  </si>
+  <si>
+    <t>超级技能ID</t>
+  </si>
+  <si>
+    <t>特殊技能ID</t>
   </si>
   <si>
     <t xml:space="preserve">1 级基础生命值
@@ -150,109 +150,113 @@
 4 非常快</t>
   </si>
   <si>
-    <t xml:space="preserve">解锁价格</t>
-  </si>
-  <si>
-    <t xml:space="preserve">碰撞半径</t>
-  </si>
-  <si>
-    <t xml:space="preserve">碰撞高度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">初始英雄等级，至少1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪莉</t>
+    <t>解锁价格</t>
+  </si>
+  <si>
+    <t>碰撞半径</t>
+  </si>
+  <si>
+    <t>碰撞高度</t>
+  </si>
+  <si>
+    <t>初始英雄等级，至少1</t>
+  </si>
+  <si>
+    <t>雪莉</t>
   </si>
   <si>
     <r>
       <rPr>
+        <rFont val="Noto Sans SC"/>
+        <charset val="1"/>
+        <family val="2"/>
         <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">雪莉是最棒的巡逻员：可靠、顽强、擅长使用霰弹枪。她实在不明白柯尔特为什么一定要抢她的风头</t>
+      <t>雪莉是最棒的巡逻员：可靠、顽强、擅长使用霰弹枪。她实在不明白柯尔特为什么一定要抢她的风头</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">......</t>
+      <t>......</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">BasicFemaleDefault</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公牛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公牛没有年轻时那么无忧无虑，也没有那么爱惹事了。但如果有人敢挑衅，他还是会毫不犹豫地把他们撞飞！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BasicMaleDefault</t>
-  </si>
-  <si>
-    <t xml:space="preserve">武士</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这是个武士</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SamuraiDefault</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柯尔特</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柯尔特是型秒乐园的大明星！他英俊潇洒，魅力四射，还会花式转枪，这些让他赢得了所有观众的心，不过雪莉除外。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VeteranDefault</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡尔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">牛逼卡尔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChickenDefault</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾尔·普里莫</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾尔·普里莫以迅雷之势连续打出4记愤怒铁拳。这墨西哥劲辣红椒味的拳头可以把对手打得满地找牙！</t>
+    <t>BasicFemaleDefault</t>
+  </si>
+  <si>
+    <t>公牛</t>
+  </si>
+  <si>
+    <t>公牛没有年轻时那么无忧无虑，也没有那么爱惹事了。但如果有人敢挑衅，他还是会毫不犹豫地把他们撞飞！</t>
+  </si>
+  <si>
+    <t>BasicMaleDefault</t>
+  </si>
+  <si>
+    <t>武士</t>
+  </si>
+  <si>
+    <t>这是个武士</t>
+  </si>
+  <si>
+    <t>SamuraiDefault</t>
+  </si>
+  <si>
+    <t>柯尔特</t>
+  </si>
+  <si>
+    <t>柯尔特是型秒乐园的大明星！他英俊潇洒，魅力四射，还会花式转枪，这些让他赢得了所有观众的心，不过雪莉除外。</t>
+  </si>
+  <si>
+    <t>VeteranDefault</t>
+  </si>
+  <si>
+    <t>卡尔</t>
+  </si>
+  <si>
+    <t>牛逼卡尔</t>
+  </si>
+  <si>
+    <t>ChickenDefault</t>
+  </si>
+  <si>
+    <t>艾尔·普里莫</t>
+  </si>
+  <si>
+    <t>艾尔·普里莫以迅雷之势连续打出4记愤怒铁拳。这墨西哥劲辣红椒味的拳头可以把对手打得满地找牙！</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>桩</t>
+  </si>
+  <si>
+    <t>短暂蓄力后旋转攻击周围敌人。可移动蓄力，可隔墙命中，不破坏墙和草。</t>
+  </si>
+  <si>
+    <t>BasicMaleNoWeaponDefault</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -266,7 +270,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -274,7 +278,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -293,12 +297,6 @@
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
       <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -334,7 +332,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border diagonalUp="1" diagonalDown="1">
       <left/>
       <right/>
       <top/>
@@ -342,97 +340,52 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellStyleXfs count="7">
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal" xfId="20"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="Normal" xfId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -667,27 +620,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="26.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="11.53"/>
+    <col min="1" max="2" width="16" customWidth="1" style="1"/>
+    <col min="3" max="3" width="11.54" customWidth="1" style="1"/>
+    <col min="4" max="5" width="26" customWidth="1" style="2"/>
+    <col min="6" max="6" width="14.33" customWidth="1" style="1"/>
+    <col min="7" max="7" width="16.27" customWidth="1" style="1"/>
+    <col min="8" max="8" width="21.28" customWidth="1" style="1"/>
+    <col min="9" max="12" width="18" customWidth="1" style="1"/>
+    <col min="13" max="13" width="26.57" customWidth="1" style="1"/>
+    <col min="14" max="16" width="18" customWidth="1" style="1"/>
+    <col min="17" max="17" width="21.14" customWidth="1" style="1"/>
+    <col min="16382" max="16384" width="11.53" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -740,7 +693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
@@ -793,7 +746,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
@@ -820,7 +773,7 @@
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
     </row>
-    <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="121.6" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>23</v>
       </c>
@@ -873,8 +826,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="n">
+    <row r="5" ht="49.25">
+      <c r="B5" s="1">
         <v>101</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -886,45 +839,45 @@
       <c r="E5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="1">
         <v>10101</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="I5" s="1">
         <v>10102</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="1">
         <v>10103</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5" s="1">
         <v>3900</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="L5" s="1">
         <v>390</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="1">
         <v>3</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="1">
         <v>0</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5" s="1">
         <v>0.3</v>
       </c>
-      <c r="P5" s="1" t="n">
+      <c r="P5" s="1">
         <v>1.2</v>
       </c>
-      <c r="Q5" s="1" t="n">
+      <c r="Q5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="n">
+    <row r="6" ht="49.25">
+      <c r="B6" s="1">
         <v>201</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -936,45 +889,45 @@
       <c r="E6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="1">
         <v>2</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="1">
         <v>20101</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="I6" s="1">
         <v>20102</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="1">
         <v>20103</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="1">
         <v>5000</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="L6" s="1">
         <v>500</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="1">
         <v>2</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="1">
         <v>10</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6" s="1">
         <v>0.3</v>
       </c>
-      <c r="P6" s="1" t="n">
+      <c r="P6" s="1">
         <v>1.2</v>
       </c>
-      <c r="Q6" s="1" t="n">
+      <c r="Q6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="n">
+    <row r="7" ht="15">
+      <c r="B7" s="1">
         <v>301</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -986,45 +939,45 @@
       <c r="E7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="1">
         <v>3</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>7</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="1">
         <v>30101</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="I7" s="1">
         <v>30102</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="1">
         <v>30103</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="K7" s="1">
         <v>3500</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="L7" s="1">
         <v>350</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="1">
         <v>4</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="1">
         <v>20</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="1">
         <v>0.3</v>
       </c>
-      <c r="P7" s="1" t="n">
+      <c r="P7" s="1">
         <v>1.2</v>
       </c>
-      <c r="Q7" s="1" t="n">
+      <c r="Q7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
+    <row r="8" ht="49.25">
+      <c r="B8" s="1">
         <v>401</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1036,45 +989,45 @@
       <c r="E8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="1">
         <v>3</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>4</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="1">
         <v>40101</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="I8" s="1">
         <v>40102</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="1">
         <v>40103</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="K8" s="1">
         <v>4000</v>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="L8" s="1">
         <v>400</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="M8" s="1">
         <v>4</v>
       </c>
-      <c r="N8" s="1" t="n">
+      <c r="N8" s="1">
         <v>30</v>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="O8" s="1">
         <v>0.3</v>
       </c>
-      <c r="P8" s="1" t="n">
+      <c r="P8" s="1">
         <v>1.2</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="Q8" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="n">
+    <row r="9" ht="15">
+      <c r="B9" s="1">
         <v>1001</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1086,45 +1039,45 @@
       <c r="E9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="1">
         <v>6</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>6</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="1">
         <v>1001001</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9" s="1">
         <v>1001002</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="1">
         <v>1001003</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="K9" s="1">
         <v>4500</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="L9" s="1">
         <v>450</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="M9" s="1">
         <v>1</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="N9" s="1">
         <v>100</v>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="O9" s="1">
         <v>0.3</v>
       </c>
-      <c r="P9" s="1" t="n">
+      <c r="P9" s="1">
         <v>1.2</v>
       </c>
-      <c r="Q9" s="1" t="n">
+      <c r="Q9" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="n">
+    <row r="10" ht="49.25">
+      <c r="B10" s="1">
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1132,6 +1085,59 @@
       </c>
       <c r="D10" s="12" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="1">
+        <v>501</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>50101</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>3900</v>
+      </c>
+      <c r="L11" s="1">
+        <v>390</v>
+      </c>
+      <c r="M11" s="1">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1143,4 +1149,9 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>